--- a/samples/04_hoa_don_dien_tu.xlsx
+++ b/samples/04_hoa_don_dien_tu.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="DanhSach" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>MST người bán</t>
+          <t>Mã số thuế người bán</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -429,7 +429,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Ngày hóa đơn</t>
+          <t>Ngày lập</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -446,7 +446,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0101234567</t>
+          <t>0301224067</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -456,7 +456,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2020-10-23</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -465,13 +465,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0312345678</t>
+          <t>0312816241</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -481,7 +481,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2021-02-20</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -496,7 +496,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0312345678</t>
+          <t>0313025323</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -506,7 +506,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2022-04-10</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">

--- a/samples/04_hoa_don_dien_tu.xlsx
+++ b/samples/04_hoa_don_dien_tu.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="DanhSach" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DanhSach" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,134 +413,166 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Mã số thuế người bán</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Số hóa đơn</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Ngày lập</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Trạng thái hóa đơn</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Tổng tiền thuế</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>0301224067</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2020-10-23</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Đã cấp mã hóa đơn</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>0312816241</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2021-02-20</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Hóa đơn bị thay thế</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>500000</v>
+          <t>DANH SÁCH HÓA ĐƠN</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0313025323</t>
+          <t>STT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>Ký hiệu mẫu số</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2021-03-01</t>
+          <t>Ký hiệu hóa đơn</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Đã cấp mã hóa đơn</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>250000</v>
+          <t>Số hóa đơn</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Ngày lập</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>MST người bán</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Tên người bán</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Tổng tiền thuế</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tổng tiền thanh toán</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Trạng thái hóa đơn</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>15/01/2022</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0301224067</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>525000</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>20/02/2022</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0312816241</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>500000</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Hóa đơn đã bị thay thế</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>01/03/2022</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0313025323</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>250000</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>789</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>10/04/2022</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>0400111222</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>789</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2022-04-10</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Hóa đơn đã bị xóa bỏ</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>800000</v>
+      <c r="M8" t="n">
+        <v>300000</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Hóa đơn đã bị xóa bỏ/hủy bỏ</t>
+        </is>
       </c>
     </row>
   </sheetData>
